--- a/artfynd/A 58410-2025 artfynd.xlsx
+++ b/artfynd/A 58410-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9020,6 +9020,112 @@
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>130828395</v>
+      </c>
+      <c r="B81" t="n">
+        <v>93092</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kilkoksjön, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>752191</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7366009</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58410-2025 artfynd.xlsx
+++ b/artfynd/A 58410-2025 artfynd.xlsx
@@ -9025,7 +9025,7 @@
         <v>130828395</v>
       </c>
       <c r="B81" t="n">
-        <v>93092</v>
+        <v>93093</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 58410-2025 artfynd.xlsx
+++ b/artfynd/A 58410-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61570077</v>
+        <v>114045682</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752046.3831070773</v>
+        <v>752077</v>
       </c>
       <c r="R2" t="n">
-        <v>7366313.378896441</v>
+        <v>7366474</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,64 +754,62 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61570078</v>
+        <v>61570079</v>
       </c>
       <c r="B3" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752046.3831070773</v>
+        <v>752136</v>
       </c>
       <c r="R3" t="n">
-        <v>7366313.378896441</v>
+        <v>7366315</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +850,9 @@
           <t>2016-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61570100</v>
+        <v>61570101</v>
       </c>
       <c r="B4" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>232140</v>
+        <v>149</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,7 +919,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -963,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752218.4466190769</v>
+        <v>752266</v>
       </c>
       <c r="R4" t="n">
-        <v>7366361.654216832</v>
+        <v>7366360</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,19 +962,9 @@
           <t>2016-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61570101</v>
+        <v>61712604</v>
       </c>
       <c r="B5" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752265.5117417411</v>
+        <v>752421</v>
       </c>
       <c r="R5" t="n">
-        <v>7366360.246737944</v>
+        <v>7366005</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1120,22 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,49 +1100,48 @@
           <t>Lars Sundberg, Sonja Kuoljok</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61570098</v>
+        <v>61712613</v>
       </c>
       <c r="B6" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>149</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1209,13 +1149,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752218.4466190769</v>
+        <v>752456</v>
       </c>
       <c r="R6" t="n">
-        <v>7366361.654216832</v>
+        <v>7365998</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1179,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,23 +1208,14 @@
           <t>Lars Sundberg, Sonja Kuoljok</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61570079</v>
+        <v>114045588</v>
       </c>
       <c r="B7" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,30 +1240,20 @@
           <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752136.1024039149</v>
+        <v>751923</v>
       </c>
       <c r="R7" t="n">
-        <v>7366314.606646643</v>
+        <v>7366456</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,22 +1277,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,38 +1291,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61712584</v>
+        <v>114045616</v>
       </c>
       <c r="B8" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,47 +1320,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>232140</v>
+        <v>149</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752329.9841195001</v>
+        <v>752149</v>
       </c>
       <c r="R8" t="n">
-        <v>7366027.331970202</v>
+        <v>7366180</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1493,22 +1374,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-09-30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-09-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,82 +1388,66 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61712412</v>
+        <v>114045641</v>
       </c>
       <c r="B9" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>149</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752237.6476987726</v>
+        <v>752188</v>
       </c>
       <c r="R9" t="n">
-        <v>7366054.968947983</v>
+        <v>7366014</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1616,22 +1471,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-09-30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,34 +1485,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>61712594</v>
+        <v>114045678</v>
       </c>
       <c r="B10" t="n">
-        <v>90130</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,47 +1514,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1958</v>
+        <v>149</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752372.9265483367</v>
+        <v>752239</v>
       </c>
       <c r="R10" t="n">
-        <v>7366017.871767183</v>
+        <v>7365985</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,22 +1568,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-09-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-09-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,34 +1582,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>61712613</v>
+        <v>114483406</v>
       </c>
       <c r="B11" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,30 +1628,20 @@
           <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Kilkok 6, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752456.0750518785</v>
+        <v>751965</v>
       </c>
       <c r="R11" t="n">
-        <v>7365997.897186085</v>
+        <v>7366262</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1862,22 +1665,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-09-30</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2016-09-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1886,34 +1679,38 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>med Överståndare</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>61712604</v>
+        <v>114494555</v>
       </c>
       <c r="B12" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,30 +1735,23 @@
           <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Kilkok 9, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752421.0124598388</v>
+        <v>752117</v>
       </c>
       <c r="R12" t="n">
-        <v>7366005.2386975</v>
+        <v>7366453</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1985,22 +1775,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-09-30</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-09-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,30 +1793,30 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114045603</v>
+        <v>114500636</v>
       </c>
       <c r="B13" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,34 +1824,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6276</v>
+        <v>149</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkok 13, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752025</v>
+        <v>752057</v>
       </c>
       <c r="R13" t="n">
-        <v>7366537</v>
+        <v>7366386</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2098,12 +1881,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,55 +1895,56 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114045741</v>
+        <v>114045764</v>
       </c>
       <c r="B14" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2170,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752005</v>
+        <v>752172</v>
       </c>
       <c r="R14" t="n">
-        <v>7366505</v>
+        <v>7366401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2232,53 +2016,58 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114045637</v>
+        <v>61570064</v>
       </c>
       <c r="B15" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752046</v>
+        <v>751996</v>
       </c>
       <c r="R15" t="n">
-        <v>7366516</v>
+        <v>7366299</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2302,12 +2091,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,33 +2105,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114045686</v>
+        <v>61712594</v>
       </c>
       <c r="B16" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,37 +2139,47 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>1958</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751893</v>
+        <v>752373</v>
       </c>
       <c r="R16" t="n">
-        <v>7366291</v>
+        <v>7366018</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2404,12 +2203,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,33 +2217,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114045638</v>
+        <v>61570098</v>
       </c>
       <c r="B17" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,37 +2247,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751966</v>
+        <v>752218</v>
       </c>
       <c r="R17" t="n">
-        <v>7366492</v>
+        <v>7366362</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2506,12 +2303,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,33 +2317,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114045735</v>
+        <v>61712412</v>
       </c>
       <c r="B18" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,37 +2351,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752439</v>
+        <v>752238</v>
       </c>
       <c r="R18" t="n">
-        <v>7365904</v>
+        <v>7366055</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2608,12 +2415,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,33 +2429,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114045606</v>
+        <v>114045698</v>
       </c>
       <c r="B19" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,21 +2459,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2680,10 +2483,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752151</v>
+        <v>751890</v>
       </c>
       <c r="R19" t="n">
-        <v>7365988</v>
+        <v>7366292</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,12 +2513,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,44 +2538,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114045713</v>
+        <v>114045706</v>
       </c>
       <c r="B20" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752438</v>
+        <v>752212</v>
       </c>
       <c r="R20" t="n">
-        <v>7365906</v>
+        <v>7366352</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,37 +2642,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114045671</v>
+        <v>114045740</v>
       </c>
       <c r="B21" t="n">
-        <v>91651</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2884,10 +2677,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752091</v>
+        <v>751922</v>
       </c>
       <c r="R21" t="n">
-        <v>7366492</v>
+        <v>7366176</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,12 +2707,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,22 +2732,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114045651</v>
+        <v>61570067</v>
       </c>
       <c r="B22" t="n">
-        <v>91651</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,37 +2750,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>232140</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752172</v>
+        <v>751996</v>
       </c>
       <c r="R22" t="n">
-        <v>7365972</v>
+        <v>7366299</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3016,12 +2806,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,33 +2820,33 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114045585</v>
+        <v>61570078</v>
       </c>
       <c r="B23" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,37 +2854,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751949</v>
+        <v>752046</v>
       </c>
       <c r="R23" t="n">
-        <v>7366299</v>
+        <v>7366313</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3118,12 +2910,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3132,55 +2924,55 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114045747</v>
+        <v>114045647</v>
       </c>
       <c r="B24" t="n">
-        <v>91591</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +2982,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751901</v>
+        <v>752005</v>
       </c>
       <c r="R24" t="n">
-        <v>7366536</v>
+        <v>7366466</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3220,12 +3012,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3245,44 +3037,39 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>114045654</v>
+        <v>114045741</v>
       </c>
       <c r="B25" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3292,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751887</v>
+        <v>752005</v>
       </c>
       <c r="R25" t="n">
-        <v>7366299</v>
+        <v>7366505</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3322,12 +3109,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,44 +3134,39 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>114045589</v>
+        <v>114045744</v>
       </c>
       <c r="B26" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3394,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752004</v>
+        <v>751886</v>
       </c>
       <c r="R26" t="n">
-        <v>7366508</v>
+        <v>7366325</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3424,12 +3206,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3449,57 +3231,55 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>114045694</v>
+        <v>114406649</v>
       </c>
       <c r="B27" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkok 1, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>751889</v>
+        <v>752145</v>
       </c>
       <c r="R27" t="n">
-        <v>7366190</v>
+        <v>7366435</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,12 +3306,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3540,55 +3320,61 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>äldre,90 år</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>114045678</v>
+        <v>114045747</v>
       </c>
       <c r="B28" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3598,10 +3384,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752239</v>
+        <v>751901</v>
       </c>
       <c r="R28" t="n">
-        <v>7365985</v>
+        <v>7366536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,50 +3446,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>114045674</v>
+        <v>114494552</v>
       </c>
       <c r="B29" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkok 10, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752393</v>
+        <v>752166</v>
       </c>
       <c r="R29" t="n">
-        <v>7366007</v>
+        <v>7366408</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3730,12 +3514,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3744,68 +3528,72 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>114045737</v>
+        <v>114494566</v>
       </c>
       <c r="B30" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkok 7, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752333</v>
+        <v>752174</v>
       </c>
       <c r="R30" t="n">
-        <v>7365957</v>
+        <v>7366387</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3832,12 +3620,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3846,71 +3634,82 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>114045588</v>
+        <v>61570069</v>
       </c>
       <c r="B31" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>751923</v>
+        <v>751996</v>
       </c>
       <c r="R31" t="n">
-        <v>7366456</v>
+        <v>7366299</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3934,12 +3733,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3948,55 +3747,55 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>114045676</v>
+        <v>114045596</v>
       </c>
       <c r="B32" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +3805,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752254</v>
+        <v>752096</v>
       </c>
       <c r="R32" t="n">
-        <v>7366333</v>
+        <v>7366461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4036,12 +3835,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4061,44 +3860,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>114045587</v>
+        <v>114045599</v>
       </c>
       <c r="B33" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4108,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>752382</v>
+        <v>752454</v>
       </c>
       <c r="R33" t="n">
-        <v>7366001</v>
+        <v>7365976</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4170,15 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>114045670</v>
+        <v>114045606</v>
       </c>
       <c r="B34" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4186,21 +3975,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4210,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>751859</v>
+        <v>752151</v>
       </c>
       <c r="R34" t="n">
-        <v>7366314</v>
+        <v>7365988</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4272,37 +4061,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>114045617</v>
+        <v>114045636</v>
       </c>
       <c r="B35" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4312,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>752289</v>
+        <v>752362</v>
       </c>
       <c r="R35" t="n">
-        <v>7366061</v>
+        <v>7366025</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,37 +4158,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>114045696</v>
+        <v>114045642</v>
       </c>
       <c r="B36" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4414,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>751998</v>
+        <v>752232</v>
       </c>
       <c r="R36" t="n">
-        <v>7366514</v>
+        <v>7366131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4444,12 +4223,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4469,44 +4248,39 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>114045597</v>
+        <v>114045652</v>
       </c>
       <c r="B37" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4516,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>752310</v>
+        <v>751974</v>
       </c>
       <c r="R37" t="n">
-        <v>7366081</v>
+        <v>7366291</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,37 +4352,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>114045645</v>
+        <v>114045669</v>
       </c>
       <c r="B38" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>752026</v>
+        <v>752138</v>
       </c>
       <c r="R38" t="n">
-        <v>7366040</v>
+        <v>7366204</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4680,37 +4449,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>114045727</v>
+        <v>114045717</v>
       </c>
       <c r="B39" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4720,10 +4484,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>752188</v>
+        <v>751998</v>
       </c>
       <c r="R39" t="n">
-        <v>7366005</v>
+        <v>7366510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4782,15 +4546,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>114045599</v>
+        <v>114045720</v>
       </c>
       <c r="B40" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>752454</v>
+        <v>751901</v>
       </c>
       <c r="R40" t="n">
-        <v>7365976</v>
+        <v>7366539</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4852,12 +4611,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4877,22 +4636,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>114045593</v>
+        <v>114045742</v>
       </c>
       <c r="B41" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4900,21 +4654,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4924,10 +4678,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>752086</v>
+        <v>751885</v>
       </c>
       <c r="R41" t="n">
-        <v>7366347</v>
+        <v>7366322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4954,12 +4708,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4979,44 +4733,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>114045612</v>
+        <v>114045765</v>
       </c>
       <c r="B42" t="n">
-        <v>91651</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>232140</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5026,10 +4775,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>752362</v>
+        <v>752333</v>
       </c>
       <c r="R42" t="n">
-        <v>7366025</v>
+        <v>7365950</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5056,12 +4805,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5081,22 +4830,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>114045634</v>
+        <v>61570068</v>
       </c>
       <c r="B43" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5122,19 +4866,21 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>752076</v>
+        <v>751996</v>
       </c>
       <c r="R43" t="n">
-        <v>7366220</v>
+        <v>7366299</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5158,12 +4904,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5172,71 +4918,73 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>114045641</v>
+        <v>61570077</v>
       </c>
       <c r="B44" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>752188</v>
+        <v>752046</v>
       </c>
       <c r="R44" t="n">
-        <v>7366014</v>
+        <v>7366313</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5260,12 +5008,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5274,55 +5022,55 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>114045613</v>
+        <v>114045582</v>
       </c>
       <c r="B45" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5332,10 +5080,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>752062</v>
+        <v>752545</v>
       </c>
       <c r="R45" t="n">
-        <v>7366374</v>
+        <v>7365999</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5394,15 +5142,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>114045624</v>
+        <v>114045593</v>
       </c>
       <c r="B46" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5410,21 +5153,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5434,10 +5177,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>751977</v>
+        <v>752086</v>
       </c>
       <c r="R46" t="n">
-        <v>7366125</v>
+        <v>7366347</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5496,37 +5239,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>114045656</v>
+        <v>114045634</v>
       </c>
       <c r="B47" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5536,10 +5274,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752036</v>
+        <v>752076</v>
       </c>
       <c r="R47" t="n">
-        <v>7366517</v>
+        <v>7366220</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,15 +5336,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>114045718</v>
+        <v>114045637</v>
       </c>
       <c r="B48" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,10 +5371,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751998</v>
+        <v>752046</v>
       </c>
       <c r="R48" t="n">
-        <v>7366510</v>
+        <v>7366516</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5668,12 +5401,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5693,44 +5426,39 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>114045660</v>
+        <v>114045638</v>
       </c>
       <c r="B49" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5740,10 +5468,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>752469</v>
+        <v>751966</v>
       </c>
       <c r="R49" t="n">
-        <v>7365990</v>
+        <v>7366492</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5802,37 +5530,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>114045709</v>
+        <v>114045639</v>
       </c>
       <c r="B50" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5842,10 +5565,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751999</v>
+        <v>751995</v>
       </c>
       <c r="R50" t="n">
-        <v>7366513</v>
+        <v>7366156</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5872,12 +5595,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5897,22 +5620,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>114045665</v>
+        <v>114045649</v>
       </c>
       <c r="B51" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5944,10 +5662,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751850</v>
+        <v>752169</v>
       </c>
       <c r="R51" t="n">
-        <v>7366327</v>
+        <v>7365978</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6006,15 +5724,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>114045691</v>
+        <v>114045650</v>
       </c>
       <c r="B52" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,10 +5759,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751889</v>
+        <v>752260</v>
       </c>
       <c r="R52" t="n">
-        <v>7366330</v>
+        <v>7366100</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6076,12 +5789,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6101,44 +5814,39 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>114045598</v>
+        <v>114045665</v>
       </c>
       <c r="B53" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6148,10 +5856,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752169</v>
+        <v>751850</v>
       </c>
       <c r="R53" t="n">
-        <v>7365978</v>
+        <v>7366327</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,15 +5918,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>114045715</v>
+        <v>114045670</v>
       </c>
       <c r="B54" t="n">
-        <v>91649</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6226,21 +5929,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6250,10 +5953,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>752333</v>
+        <v>751859</v>
       </c>
       <c r="R54" t="n">
-        <v>7365957</v>
+        <v>7366314</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6280,12 +5983,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6305,44 +6008,39 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>114045666</v>
+        <v>114045691</v>
       </c>
       <c r="B55" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6352,10 +6050,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>752083</v>
+        <v>751889</v>
       </c>
       <c r="R55" t="n">
-        <v>7366513</v>
+        <v>7366330</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6382,12 +6080,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6407,22 +6105,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>114045636</v>
+        <v>114045694</v>
       </c>
       <c r="B56" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6430,21 +6123,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6454,10 +6147,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>752362</v>
+        <v>751889</v>
       </c>
       <c r="R56" t="n">
-        <v>7366025</v>
+        <v>7366190</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6484,12 +6177,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6509,22 +6202,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>114045717</v>
+        <v>114045695</v>
       </c>
       <c r="B57" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,21 +6220,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6556,10 +6244,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751998</v>
+        <v>752591</v>
       </c>
       <c r="R57" t="n">
-        <v>7366510</v>
+        <v>7366061</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,15 +6306,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>114045649</v>
+        <v>114045718</v>
       </c>
       <c r="B58" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6658,10 +6341,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>752169</v>
+        <v>751998</v>
       </c>
       <c r="R58" t="n">
-        <v>7365978</v>
+        <v>7366510</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6688,12 +6371,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6713,22 +6396,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>114045720</v>
+        <v>114045721</v>
       </c>
       <c r="B59" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6736,21 +6414,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6760,10 +6438,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>751901</v>
+        <v>751968</v>
       </c>
       <c r="R59" t="n">
-        <v>7366539</v>
+        <v>7366144</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6822,15 +6500,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>114045765</v>
+        <v>114045735</v>
       </c>
       <c r="B60" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6838,21 +6511,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6862,10 +6535,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>752333</v>
+        <v>752439</v>
       </c>
       <c r="R60" t="n">
-        <v>7365950</v>
+        <v>7365904</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6924,15 +6597,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>114045721</v>
+        <v>114045750</v>
       </c>
       <c r="B61" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6964,10 +6632,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751968</v>
+        <v>751727</v>
       </c>
       <c r="R61" t="n">
-        <v>7366144</v>
+        <v>7366304</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,15 +6694,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>114045639</v>
+        <v>114483408</v>
       </c>
       <c r="B62" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7062,14 +6725,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkok 4, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>751995</v>
+        <v>751979</v>
       </c>
       <c r="R62" t="n">
-        <v>7366156</v>
+        <v>7366119</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7096,12 +6759,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7112,53 +6775,53 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>114045772</v>
+        <v>114045587</v>
       </c>
       <c r="B63" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7168,10 +6831,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>752434</v>
+        <v>752382</v>
       </c>
       <c r="R63" t="n">
-        <v>7365921</v>
+        <v>7366001</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7198,12 +6861,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7223,22 +6886,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>114045647</v>
+        <v>114045617</v>
       </c>
       <c r="B64" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7246,21 +6904,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7270,10 +6928,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>752005</v>
+        <v>752289</v>
       </c>
       <c r="R64" t="n">
-        <v>7366466</v>
+        <v>7366061</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7332,37 +6990,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>114045685</v>
+        <v>114045654</v>
       </c>
       <c r="B65" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7372,10 +7025,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751874</v>
+        <v>751887</v>
       </c>
       <c r="R65" t="n">
-        <v>7366364</v>
+        <v>7366299</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7402,12 +7055,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7427,22 +7080,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>114045750</v>
+        <v>114045660</v>
       </c>
       <c r="B66" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7450,21 +7098,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7474,10 +7122,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751727</v>
+        <v>752469</v>
       </c>
       <c r="R66" t="n">
-        <v>7366304</v>
+        <v>7365990</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7504,12 +7152,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7529,44 +7177,39 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>114045744</v>
+        <v>114045585</v>
       </c>
       <c r="B67" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>4365</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7576,10 +7219,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>751886</v>
+        <v>751949</v>
       </c>
       <c r="R67" t="n">
-        <v>7366325</v>
+        <v>7366299</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7606,12 +7249,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7631,22 +7274,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>114045610</v>
+        <v>114045645</v>
       </c>
       <c r="B68" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7654,21 +7292,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7678,10 +7316,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>752440</v>
+        <v>752026</v>
       </c>
       <c r="R68" t="n">
-        <v>7365997</v>
+        <v>7366040</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7743,12 +7381,7 @@
         <v>114045657</v>
       </c>
       <c r="B69" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7842,37 +7475,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>114045740</v>
+        <v>114045674</v>
       </c>
       <c r="B70" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7882,10 +7510,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751922</v>
+        <v>752393</v>
       </c>
       <c r="R70" t="n">
-        <v>7366176</v>
+        <v>7366007</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7912,12 +7540,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7937,44 +7565,39 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>114045706</v>
+        <v>114045676</v>
       </c>
       <c r="B71" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7984,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>752212</v>
+        <v>752254</v>
       </c>
       <c r="R71" t="n">
-        <v>7366352</v>
+        <v>7366333</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8046,37 +7669,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>114045698</v>
+        <v>114045685</v>
       </c>
       <c r="B72" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8086,10 +7704,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751890</v>
+        <v>751874</v>
       </c>
       <c r="R72" t="n">
-        <v>7366292</v>
+        <v>7366364</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8148,37 +7766,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>114045726</v>
+        <v>114045727</v>
       </c>
       <c r="B73" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8188,10 +7801,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751883</v>
+        <v>752188</v>
       </c>
       <c r="R73" t="n">
-        <v>7366326</v>
+        <v>7366005</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8250,37 +7863,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>114045742</v>
+        <v>114045772</v>
       </c>
       <c r="B74" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8290,10 +7898,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751885</v>
+        <v>752434</v>
       </c>
       <c r="R74" t="n">
-        <v>7366322</v>
+        <v>7365921</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8352,53 +7960,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>114406648</v>
+        <v>114045589</v>
       </c>
       <c r="B75" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kilkok 2, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751933</v>
+        <v>752004</v>
       </c>
       <c r="R75" t="n">
-        <v>7366305</v>
+        <v>7366508</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8425,12 +8025,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8439,44 +8039,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>äldre, ca 100 år</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>114483408</v>
+        <v>114045597</v>
       </c>
       <c r="B76" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8484,34 +8068,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kilkok 4, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751979</v>
+        <v>752310</v>
       </c>
       <c r="R76" t="n">
-        <v>7366119</v>
+        <v>7366081</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8538,12 +8122,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8554,74 +8138,61 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>114500636</v>
+        <v>114045608</v>
       </c>
       <c r="B77" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kilkok 13, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>752057</v>
+        <v>752556</v>
       </c>
       <c r="R77" t="n">
-        <v>7366386</v>
+        <v>7365988</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8648,12 +8219,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8662,77 +8233,63 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>114500633</v>
+        <v>114045613</v>
       </c>
       <c r="B78" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kilkok 14, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751870</v>
+        <v>752062</v>
       </c>
       <c r="R78" t="n">
-        <v>7366555</v>
+        <v>7366374</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8759,12 +8316,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8773,39 +8330,28 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>114494566</v>
+        <v>114045661</v>
       </c>
       <c r="B79" t="n">
-        <v>91591</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8813,37 +8359,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kilkok 7, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>752174</v>
+        <v>752092</v>
       </c>
       <c r="R79" t="n">
-        <v>7366387</v>
+        <v>7366438</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8870,12 +8413,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8884,88 +8427,66 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122574773</v>
+        <v>114045666</v>
       </c>
       <c r="B80" t="n">
-        <v>92217</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6055</v>
+        <v>4366</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>752088</v>
+        <v>752083</v>
       </c>
       <c r="R80" t="n">
-        <v>7366376</v>
+        <v>7366513</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9003,14 +8524,13 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -9022,48 +8542,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130828395</v>
+        <v>114045696</v>
       </c>
       <c r="B81" t="n">
-        <v>93127</v>
+        <v>93209</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>232140</v>
+        <v>4366</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kilkoksjön, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>752191</v>
+        <v>751998</v>
       </c>
       <c r="R81" t="n">
-        <v>7366009</v>
+        <v>7366514</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9104,27 +8621,2433 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>114045726</v>
+      </c>
+      <c r="B82" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>751883</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7366326</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>114045630</v>
+      </c>
+      <c r="B83" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>752238</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7366109</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>114045714</v>
+      </c>
+      <c r="B84" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>752599</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7366048</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>114045624</v>
+      </c>
+      <c r="B85" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>751977</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7366125</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>122574773</v>
+      </c>
+      <c r="B86" t="n">
+        <v>93181</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>752088</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7366376</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>114045598</v>
+      </c>
+      <c r="B87" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>752169</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7365978</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>114045603</v>
+      </c>
+      <c r="B88" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>752025</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7366537</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>114045610</v>
+      </c>
+      <c r="B89" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>752440</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7365997</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>114045658</v>
+      </c>
+      <c r="B90" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>751822</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7366417</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>114045686</v>
+      </c>
+      <c r="B91" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>751893</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7366291</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>114045709</v>
+      </c>
+      <c r="B92" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>751999</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7366513</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>114045713</v>
+      </c>
+      <c r="B93" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>752438</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7365906</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>114045737</v>
+      </c>
+      <c r="B94" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>752333</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7365957</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>114045768</v>
+      </c>
+      <c r="B95" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>751821</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7366381</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>114406647</v>
+      </c>
+      <c r="B96" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Kilkok 3, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>751974</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7366258</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>äldre,ca 90 år</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>114406648</v>
+      </c>
+      <c r="B97" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Kilkok 2, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>751933</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7366305</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>äldre, ca 100 år</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>114500633</v>
+      </c>
+      <c r="B98" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Kilkok 14, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>751870</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7366555</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>114045656</v>
+      </c>
+      <c r="B99" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>752036</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7366517</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>61570100</v>
+      </c>
+      <c r="B100" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Kilkokheden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>752218</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7366362</v>
+      </c>
+      <c r="S100" t="n">
+        <v>75</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>61712584</v>
+      </c>
+      <c r="B101" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Kilkokheden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>752330</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7366027</v>
+      </c>
+      <c r="S101" t="n">
+        <v>25</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2016-09-30</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2016-09-30</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>114045612</v>
+      </c>
+      <c r="B102" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>752362</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7366025</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>114045651</v>
+      </c>
+      <c r="B103" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>752172</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7365972</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>114045671</v>
+      </c>
+      <c r="B104" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>752091</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7366492</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>130828395</v>
+      </c>
+      <c r="B105" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Kilkoksjön, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>752191</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7366009</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
           <t>Tyr Nilsson</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
+      <c r="AX105" t="inlineStr">
         <is>
           <t>Nils Bodin</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr"/>
+      <c r="AY105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58410-2025 artfynd.xlsx
+++ b/artfynd/A 58410-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY105"/>
+  <dimension ref="A1:AZ105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045682</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570079</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570101</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61712604</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61712613</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045588</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045616</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045641</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045678</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1704,6 +1754,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114483406</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114494555</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114500636</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045764</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2125,6 +2195,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570064</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2233,6 +2308,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61712594</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2337,6 +2417,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570098</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2445,6 +2530,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61712412</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2542,6 +2632,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045698</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2639,6 +2734,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045706</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2736,6 +2836,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045740</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2840,6 +2945,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570067</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2944,6 +3054,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570078</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3041,6 +3156,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045647</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3138,6 +3258,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045741</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3235,6 +3360,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045744</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3346,6 +3476,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114406649</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3443,6 +3578,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045747</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3549,6 +3689,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114494552</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3655,6 +3800,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114494566</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3767,6 +3917,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570069</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3864,6 +4019,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045596</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3961,6 +4121,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045599</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4058,6 +4223,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045606</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4155,6 +4325,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045636</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4252,6 +4427,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045642</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4349,6 +4529,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045652</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4446,6 +4631,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045669</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4543,6 +4733,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045717</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4640,6 +4835,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045720</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4737,6 +4937,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045742</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4834,6 +5039,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045765</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4938,6 +5148,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570068</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5042,6 +5257,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570077</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5139,6 +5359,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045582</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5236,6 +5461,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045593</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5333,6 +5563,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045634</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5430,6 +5665,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045637</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5527,6 +5767,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045638</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5624,6 +5869,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045639</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5721,6 +5971,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045649</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5818,6 +6073,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045650</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5915,6 +6175,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045665</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6012,6 +6277,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045670</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6109,6 +6379,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045691</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6206,6 +6481,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045694</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6303,6 +6583,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045695</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6400,6 +6685,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045718</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6497,6 +6787,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045721</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6594,6 +6889,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045735</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6691,6 +6991,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045750</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6793,6 +7098,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114483408</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6890,6 +7200,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045587</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6987,6 +7302,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045617</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7084,6 +7404,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045654</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7181,6 +7506,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045660</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7278,6 +7608,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045585</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7375,6 +7710,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045645</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7472,6 +7812,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045657</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7569,6 +7914,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045674</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7666,6 +8016,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045676</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7763,6 +8118,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045685</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7860,6 +8220,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045727</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7957,6 +8322,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045772</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8054,6 +8424,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045589</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8151,6 +8526,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045597</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8248,6 +8628,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045608</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8345,6 +8730,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045613</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8442,6 +8832,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045661</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8539,6 +8934,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045666</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8636,6 +9036,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045696</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8733,6 +9138,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045726</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8830,6 +9240,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045630</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8927,6 +9342,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045714</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9024,6 +9444,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045624</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9133,6 +9558,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122574773</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9230,6 +9660,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045598</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9327,6 +9762,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045603</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9424,6 +9864,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045610</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9521,6 +9966,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045658</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9618,6 +10068,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045686</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9715,6 +10170,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045709</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9812,6 +10272,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045713</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9909,6 +10374,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045737</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10006,6 +10476,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045768</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10117,6 +10592,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114406647</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10228,6 +10708,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114406648</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10334,6 +10819,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114500633</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10431,6 +10921,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045656</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10543,6 +11038,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570100</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10651,6 +11151,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61712584</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10748,6 +11253,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045612</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10845,6 +11355,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045651</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10942,6 +11457,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045671</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11048,8 +11568,119 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130828395</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>